--- a/entorno/mir-v2/archivos_de_prueba/Chubut_con_errores/MPE_2026_T1_Chubut_CON_ERRORES.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chubut_con_errores/MPE_2026_T1_Chubut_CON_ERRORES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MPE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="LISTAS" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="ERRORES_ESPERADOS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERRORES_ESPERADOS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -209,7 +209,6 @@
         <t>Apellido/s
 Qué se espera: texto
 Máximo 20 caracteres.
-Elegir de la lista "Provincias".
 Campo obligatorio.</t>
       </text>
     </comment>
@@ -983,7 +982,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Villalba</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1130,7 +1129,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Villalba</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1273,12 +1272,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CABA</t>
+          <t>Ojeda</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bautista</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1288,20 +1287,20 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Justicia</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>46159</v>
+        <v>45737</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Encuentro espontáneo</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1316,12 +1315,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Sí</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1401,7 +1400,7 @@
         </is>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>46185</v>
+        <v>45763</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1416,7 +1415,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Díaz</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1563,7 +1562,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>La Pampa</t>
+          <t>Sosa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1710,7 +1709,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Formosa</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1853,7 +1852,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ledesma</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1996,7 +1995,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Quiroga</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2139,7 +2138,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CABA</t>
+          <t>Gómez</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2282,7 +2281,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Santiago del Estero</t>
+          <t>Villalba</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2425,12 +2424,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>La Pampa</t>
+          <t>Paz</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Thiago</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2440,20 +2439,20 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juzgado</t>
+          <t>Encuentro espontáneo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OPN</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>46001</v>
+        <v>46043</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2468,14 +2467,14 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>Familia ampliada</t>
@@ -2488,18 +2487,18 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="P14" s="4" t="n">
         <v>11</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2509,7 +2508,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Familia Ojeda</t>
+          <t>Familia Ledesma</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2524,36 +2523,36 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Adopción</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Jardín de infantes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Universitario completo</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AC14" s="5" t="n">
-        <v>46092</v>
+        <v>46212</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2568,12 +2567,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Neuquén</t>
+          <t>Romero</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2583,22 +2582,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Policía</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>46231</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>OPN</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>45597</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>Dato 12</t>
@@ -2616,7 +2615,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2626,23 +2625,23 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
+          <t>Hogar Los Álamos</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>Programa de Acompañamiento Sur</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="P15" s="4" t="n">
         <v>12</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2652,7 +2651,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Familia Martínez</t>
+          <t>Familia Ojeda</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2662,12 +2661,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Adopción</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2677,30 +2676,30 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Terciario incompleto</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Primaria completa</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="AC15" s="5" t="n">
-        <v>45661</v>
+        <v>46287</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Cese por guarda con fines de adopción</t>
+          <t>Cese por mayoría de edad CON proyecto autónomo (CON PAE)</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
@@ -2711,12 +2710,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>San Juan</t>
+          <t>Díaz</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Mateo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2731,11 +2730,11 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Justicia</t>
         </is>
       </c>
       <c r="G16" s="5" t="n">
-        <v>45733</v>
+        <v>45723</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2759,33 +2758,33 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Familia ampliada</t>
+          <t>Alojamiento formal</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="P16" s="4" t="n">
         <v>13</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2795,7 +2794,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Familia Paz</t>
+          <t>Familia Díaz</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2810,19 +2809,19 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Reintegro familiar</t>
+          <t>Adopción</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="Z16" t="inlineStr">
         <is>
           <t>No</t>
@@ -2835,11 +2834,11 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>45850</v>
+        <v>45823</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2854,12 +2853,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tierra del Fuego</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bautista</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2869,7 +2868,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Juzgado</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2878,11 +2877,11 @@
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>45788</v>
+        <v>45717</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2897,7 +2896,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2912,45 +2911,45 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="P17" s="4" t="n">
         <v>14</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
+          <t>Hogar Los Álamos</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Dato 14</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Familia Ledesma</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Dato 14</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
           <t>Hogar Nuestra Señora</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Dato 14</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Familia Gómez</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Dato 14</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
-        </is>
-      </c>
       <c r="W17" t="inlineStr">
         <is>
           <t>Reintegro familiar</t>
@@ -2958,35 +2957,35 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Nunca asistió</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Terciario completo</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="AC17" s="5" t="n">
-        <v>45829</v>
+        <v>45840</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Cese por guarda con fines de adopción</t>
+          <t>Otros motivos de cese de la MPE</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
@@ -3001,12 +3000,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Catamarca</t>
+          <t>López</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3016,7 +3015,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Juzgado</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3025,7 +3024,7 @@
         </is>
       </c>
       <c r="G18" s="5" t="n">
-        <v>45677</v>
+        <v>46096</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -3054,50 +3053,50 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
+          <t>Programa de Acompañamiento Sur</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>Hogar Los Álamos</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="P18" s="4" t="n">
         <v>15</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
+          <t>Residencia El Ceibo</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Dato 15</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Familia Ledesma</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Dato 15</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
           <t>Hogar Nuestra Señora</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Dato 15</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Familia Ledesma</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Dato 15</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Hogar Los Álamos</t>
-        </is>
-      </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>Reintegro familiar</t>
@@ -3105,35 +3104,35 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Universitario completo</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Universitario incompleto</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="AC18" s="5" t="n">
-        <v>45758</v>
+        <v>46241</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Cese por mayoría de edad CON proyecto autónomo (SIN PAE)</t>
+          <t>Otros motivos de cese de la MPE</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr"/>
@@ -3144,12 +3143,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Santiago del Estero</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bautista</t>
+          <t>Mateo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3159,20 +3158,20 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OPN</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>46015</v>
+        <v>45965</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3187,34 +3186,34 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Familia de acogimiento</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
+          <t>Centro Municipal Norte</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
           <t>Programa de Acompañamiento Sur</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="P19" s="4" t="n">
         <v>16</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -3272,7 +3271,7 @@
         </is>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>46049</v>
+        <v>45999</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3287,7 +3286,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Entre Ríos</t>
+          <t>Martínez</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3430,7 +3429,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tierra del Fuego</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3577,7 +3576,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tierra del Fuego</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3724,7 +3723,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Chaco</t>
+          <t>Fernández</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3867,12 +3866,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CABA</t>
+          <t>Paz</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4010,7 +4009,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Gómez</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4157,12 +4156,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>San Juan</t>
+          <t>Ojeda</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Martina</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4300,7 +4299,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Corrientes</t>
+          <t>Martínez</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4447,7 +4446,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Corrientes</t>
+          <t>Martínez</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4590,7 +4589,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Misiones</t>
+          <t>Romero</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4733,12 +4732,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chaco</t>
+          <t>Paz</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Benjamín</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4748,20 +4747,20 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Policía</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Justicia</t>
+          <t>OPN</t>
         </is>
       </c>
       <c r="G30" s="5" t="n">
-        <v>45603</v>
+        <v>45811</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Juzgado</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4861,7 +4860,7 @@
         </is>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>45796</v>
+        <v>46004</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4880,7 +4879,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Formosa</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5023,7 +5022,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Misiones</t>
+          <t>Romero</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5170,7 +5169,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tucumán</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5317,7 +5316,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Gómez</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5464,7 +5463,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>La Rioja</t>
+          <t>Sosa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5607,22 +5606,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>Ledesma</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Joaquín</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>20-90136863-6</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>VALOR INVENTADO</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Joaquín</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>20-90136863-6</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Otros</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6042,7 +6041,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Gómez</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -7335,10 +7334,7 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="W2:Y2"/>
   </mergeCells>
-  <dataValidations count="14">
-    <dataValidation sqref="B4:B203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Apellido/s&quot;." type="list">
-      <formula1>LISTAS!$G$2:$G$25</formula1>
-    </dataValidation>
+  <dataValidations count="13">
     <dataValidation sqref="E4:E203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Origen de la demanda&quot;." type="list">
       <formula1>LISTAS!$E$2:$E$7</formula1>
     </dataValidation>
@@ -7358,7 +7354,7 @@
       <formula1>LISTAS!$B$2:$B$5</formula1>
     </dataValidation>
     <dataValidation sqref="W4:W203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Tipo de proyecto de restitución&quot;." type="list">
-      <formula1>LISTAS!$H$2:$H$5</formula1>
+      <formula1>LISTAS!$G$2:$G$5</formula1>
     </dataValidation>
     <dataValidation sqref="X4:X203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Decreto judicial de adoptabilidad&quot;." type="list">
       <formula1>LISTAS!$F$2:$F$4</formula1>
@@ -7439,8 +7435,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Campo obligatorio.
-Debe elegirse un valor de la lista "Provincias".</t>
+          <t>Campo obligatorio.</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7818,7 +7813,6 @@
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7854,11 +7848,6 @@
       </c>
       <c r="G1" s="6" t="inlineStr">
         <is>
-          <t>Provincias</t>
-        </is>
-      </c>
-      <c r="H1" s="6" t="inlineStr">
-        <is>
           <t>Tipo de proyecto de restitución</t>
         </is>
       </c>
@@ -7896,11 +7885,6 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
           <t>Reintegro familiar</t>
         </is>
       </c>
@@ -7938,11 +7922,6 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CABA</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
           <t>Adopción</t>
         </is>
       </c>
@@ -7980,11 +7959,6 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Catamarca</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
           <t>Autonomía</t>
         </is>
       </c>
@@ -8012,11 +7986,6 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaco</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
           <t>Otros</t>
         </is>
       </c>
@@ -8037,11 +8006,6 @@
           <t>Juzgado</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8054,11 +8018,6 @@
           <t>Otros</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Córdoba</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8066,11 +8025,6 @@
           <t>Secundaria completa</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Corrientes</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8078,11 +8032,6 @@
           <t>Terciario incompleto</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Entre Ríos</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8090,11 +8039,6 @@
           <t>Terciario completo</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Formosa</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8102,11 +8046,6 @@
           <t>Universitario incompleto</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Jujuy</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8114,105 +8053,11 @@
           <t>Universitario completo</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>La Pampa</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
           <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>La Rioja</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Mendoza</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Misiones</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Neuquén</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Río Negro</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Salta</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>San Juan</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>San Luis</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Santa Fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Santiago del Estero</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Tierra del Fuego</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Tucumán</t>
         </is>
       </c>
     </row>
@@ -8325,7 +8170,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Apellido/s</t>
+          <t>Origen de la demanda</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/entorno/mir-v2/archivos_de_prueba/Chubut_con_errores/MPE_2026_T1_Chubut_CON_ERRORES.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chubut_con_errores/MPE_2026_T1_Chubut_CON_ERRORES.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,7 +111,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -201,7 +201,7 @@
       <text>
         <t>ID del Niño, niña o Adolescente
 Qué se espera: un número entero
-No es obligatorio.</t>
+Campo obligatorio.</t>
       </text>
     </comment>
     <comment ref="B3" authorId="0" shapeId="0">
@@ -822,155 +822,155 @@
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ID del Niño, niña o Adolescente</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+          <t>ID del Niño, niña o Adolescente *</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Apellido/s *</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Nombre/s *</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Cuil o documento de identidad *</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Origen de la demanda</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Organismo que toma la MPE</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Fecha de inicio MPE</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Última fecha de renovación</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Motivo de toma de MPE</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Submotivo de toma de MPE</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Elevación dictamen MPE a juzgado</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Control de legalidad por autoridad judicial</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Modalidad de cuidado</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>ID dispositivo residencial</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Nombre de la residencia/hogar *</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>ID familia</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>Familia</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>Departamento de residencia de la familia (dispositivo familiar)</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>ID familia ampliada</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>Familia Ampliada</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>Vínculo con el NyA</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>Departamento de residencia de la familia (dispositivo familiar)</t>
         </is>
       </c>
-      <c r="W3" s="2" t="inlineStr">
+      <c r="W3" s="3" t="inlineStr">
         <is>
           <t>Tipo de proyecto de restitución</t>
         </is>
       </c>
-      <c r="X3" s="2" t="inlineStr">
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>Decreto judicial de adoptabilidad</t>
         </is>
       </c>
-      <c r="Y3" s="2" t="inlineStr">
+      <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>Solicitud inclusión proy. autonomía</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="inlineStr">
+      <c r="Z3" s="3" t="inlineStr">
         <is>
           <t>¿Asiste actualmente a una institución educativa?</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>Máximo nivel educativo alcanzado</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <t>Consumo problemático de sustancias</t>
         </is>
       </c>
-      <c r="AC3" s="2" t="inlineStr">
+      <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>Fecha de cese</t>
         </is>
       </c>
-      <c r="AD3" s="2" t="inlineStr">
+      <c r="AD3" s="3" t="inlineStr">
         <is>
           <t>Motivo de cese</t>
         </is>
       </c>
-      <c r="AE3" s="2" t="inlineStr">
+      <c r="AE3" s="3" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>46005</v>
+        <v>46006</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>45737</v>
+        <v>45738</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>45763</v>
+        <v>45764</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>45689</v>
+        <v>45690</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>45706</v>
+        <v>45707</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>45720</v>
+        <v>45721</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>45788</v>
+        <v>45789</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>46074</v>
+        <v>46075</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>45757</v>
+        <v>45758</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>45816</v>
+        <v>45817</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="G16" s="5" t="n">
-        <v>45723</v>
+        <v>45724</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>45823</v>
+        <v>45824</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>45717</v>
+        <v>45718</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>45840</v>
+        <v>45841</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="G18" s="5" t="n">
-        <v>46096</v>
+        <v>46097</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="G20" s="5" t="n">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>45637</v>
+        <v>45638</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>45679</v>
+        <v>45680</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="G22" s="5" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>45651</v>
+        <v>45652</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>45831</v>
+        <v>45832</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>46082</v>
+        <v>46083</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>45692</v>
+        <v>45693</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         </is>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>45804</v>
+        <v>45805</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="G26" s="5" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         </is>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>45676</v>
+        <v>45677</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="G27" s="5" t="n">
-        <v>45593</v>
+        <v>45594</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>45707</v>
+        <v>45708</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="G28" s="5" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         </is>
       </c>
       <c r="G30" s="5" t="n">
-        <v>45811</v>
+        <v>45812</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         </is>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>46004</v>
+        <v>46005</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>45685</v>
+        <v>45686</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="G32" s="5" t="n">
-        <v>45809</v>
+        <v>45810</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>45787</v>
+        <v>45788</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="AC34" s="5" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>45619</v>
+        <v>45620</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="AC35" s="5" t="n">
-        <v>45816</v>
+        <v>45817</v>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="G36" s="5" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         </is>
       </c>
       <c r="AC36" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
@@ -5755,8 +5755,11 @@
       <c r="AC37" s="5" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
-        <v>999</v>
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ledesma</t>
+        </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5779,7 +5782,7 @@
         </is>
       </c>
       <c r="G38" s="5" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -5883,7 +5886,7 @@
         </is>
       </c>
       <c r="AC38" s="5" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
@@ -5922,7 +5925,7 @@
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>46010</v>
+        <v>46011</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -6026,7 +6029,7 @@
         </is>
       </c>
       <c r="AC39" s="5" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
@@ -6065,7 +6068,7 @@
         </is>
       </c>
       <c r="G40" s="5" t="n">
-        <v>45787</v>
+        <v>45788</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -6169,7 +6172,7 @@
         </is>
       </c>
       <c r="AC40" s="5" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
@@ -7425,7 +7428,11 @@
           <t>ID del Niño, niña o Adolescente</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n"/>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Campo obligatorio.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8220,7 +8227,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Apellido/s</t>
+          <t>ID del Niño, niña o Adolescente</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/entorno/mir-v2/archivos_de_prueba/Chubut_con_errores/MPE_2026_T1_Chubut_CON_ERRORES.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chubut_con_errores/MPE_2026_T1_Chubut_CON_ERRORES.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERRORES_ESPERADOS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="MPE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="ERRORES_ESPERADOS" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,10 +35,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -96,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -110,11 +105,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -194,257 +184,252 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>RUNAC</author>
+    <author>MIR</author>
   </authors>
   <commentList>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
-        <t>ID del Niño, niña o Adolescente
-Qué se espera: un número entero
-Campo obligatorio.</t>
+        <t>ID del niño, niña o adolescente
+Obligatorio
+Qué va: Número entero.
+Tiene que figurar en el LEGAJO_NYA del período.</t>
       </text>
     </comment>
     <comment ref="B3" authorId="0" shapeId="0">
       <text>
         <t>Apellido/s
-Qué se espera: texto
-Máximo 20 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <t>Nombre/s
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="D3" authorId="0" shapeId="0">
       <text>
         <t>Cuil o documento de identidad
-Qué se espera: texto
-Máximo 13 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 13 caracteres.
+Tiene que ser un CUIL válido: se controla el dígito verificador.
+Aviso: Con el formato NN-NNNNNNNN-N.
+Tiene que coincidir con el del LEGAJO_NYA.</t>
       </text>
     </comment>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <t>Origen de la demanda
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Origen de la demanda".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Encuentro espontáneo, Educación, Salud, Policía, Juzgado, Otros.</t>
       </text>
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <t>Organismo que toma la MPE
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Organismo que toma la MPE".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: OPN, Justicia, Otro.</t>
       </text>
     </comment>
     <comment ref="G3" authorId="0" shapeId="0">
       <text>
         <t>Fecha de inicio MPE
-Qué se espera: una fecha, con formato dd/mm/aaaa
-No es obligatorio.</t>
+Opcional
+Qué va: Fecha, como día/mes/año.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>Última fecha de renovación
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Origen de la demanda".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Encuentro espontáneo, Educación, Salud, Policía, Juzgado, Otros.</t>
       </text>
     </comment>
     <comment ref="I3" authorId="0" shapeId="0">
       <text>
         <t>Motivo de toma de MPE
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="J3" authorId="0" shapeId="0">
       <text>
         <t>Submotivo de toma de MPE
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <t>Elevación dictamen MPE a juzgado
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>Control de legalidad por autoridad judicial
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="M3" authorId="0" shapeId="0">
       <text>
         <t>Modalidad de cuidado
-Qué se espera: texto
-Máximo 22 caracteres.
-Elegir de la lista "Modalidad de cuidado".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Alojamiento formal, Familia ampliada, Familia de acogimiento, Otro.</t>
       </text>
     </comment>
     <comment ref="N3" authorId="0" shapeId="0">
       <text>
         <t>ID dispositivo residencial
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="O3" authorId="0" shapeId="0">
       <text>
         <t>Nombre de la residencia/hogar
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.
+Aviso: Tiene que figurar en el DISP_SCP del período.</t>
       </text>
     </comment>
     <comment ref="P3" authorId="0" shapeId="0">
       <text>
         <t>ID familia
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 1 y None.
+Entre 1 y 999999999.</t>
       </text>
     </comment>
     <comment ref="Q3" authorId="0" shapeId="0">
       <text>
         <t>Familia
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.</t>
       </text>
     </comment>
     <comment ref="R3" authorId="0" shapeId="0">
       <text>
         <t>Departamento de residencia de la familia (dispositivo familiar)
-Qué se espera: texto
-No es obligatorio.</t>
+Opcional
+Qué va: Texto.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <t>ID familia ampliada
-Qué se espera: texto
-No es obligatorio.</t>
+Opcional
+Qué va: Texto.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="T3" authorId="0" shapeId="0">
       <text>
         <t>Familia Ampliada
-Qué se espera: texto
-No es obligatorio.</t>
+Opcional
+Qué va: Texto.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="U3" authorId="0" shapeId="0">
       <text>
         <t>Vínculo con el NyA
-Qué se espera: texto
-No es obligatorio.</t>
+Opcional
+Qué va: Texto.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="V3" authorId="0" shapeId="0">
       <text>
         <t>Departamento de residencia de la familia (dispositivo familiar)
-Qué se espera: texto
-No es obligatorio.</t>
+Opcional
+Qué va: Texto.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="W3" authorId="0" shapeId="0">
       <text>
         <t>Tipo de proyecto de restitución
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Tipo de proyecto de restitución".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Reintegro familiar, Adopción, Autonomía, Otros.</t>
       </text>
     </comment>
     <comment ref="X3" authorId="0" shapeId="0">
       <text>
         <t>Decreto judicial de adoptabilidad
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="Y3" authorId="0" shapeId="0">
       <text>
         <t>Solicitud inclusión proy. autonomía
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="Z3" authorId="0" shapeId="0">
       <text>
         <t>¿Asiste actualmente a una institución educativa?
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="AA3" authorId="0" shapeId="0">
       <text>
         <t>Máximo nivel educativo alcanzado
-Qué se espera: texto
-Máximo 24 caracteres.
-Elegir de la lista "Máximo nivel educativo alcanzado".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 12 opciones, en el desplegable.</t>
       </text>
     </comment>
     <comment ref="AB3" authorId="0" shapeId="0">
       <text>
         <t>Consumo problemático de sustancias
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="AC3" authorId="0" shapeId="0">
       <text>
         <t>Fecha de cese
-Qué se espera: una fecha, con formato dd/mm/aaaa
-No es obligatorio.</t>
+Opcional
+Qué va: Fecha, como día/mes/año.
+Aviso: No puede ser posterior a hoy.
+"Fecha de cese" no puede ser anterior a "Fecha de inicio MPE" ()</t>
       </text>
     </comment>
     <comment ref="AD3" authorId="0" shapeId="0">
       <text>
         <t>Motivo de cese
-Qué se espera: texto
-Máximo 56 caracteres.
-Elegir de la lista "Motivo de cese".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Cese por guarda con fines de adopción, Cese por mayoría de edad CON proyecto autónomo (CON PAE), Cese por mayoría de edad CON proyecto autónomo (SIN PAE), Cese por mayoría de edad SIN proyecto autónomo, Otros motivos de cese de la MPE.</t>
       </text>
     </comment>
     <comment ref="AE3" authorId="0" shapeId="0">
       <text>
         <t>Observaciones
-Qué se espera: texto
-No es obligatorio.</t>
+Opcional
+Qué va: Texto.</t>
       </text>
     </comment>
   </commentList>
@@ -822,7 +807,7 @@
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ID del Niño, niña o Adolescente *</t>
+          <t>ID del niño, niña o adolescente *</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1006,7 +991,7 @@
         </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1110,7 +1095,7 @@
         </is>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -1153,7 +1138,7 @@
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>46062</v>
+        <v>46066</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1257,7 +1242,7 @@
         </is>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>46151</v>
+        <v>46155</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1296,7 +1281,7 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>45738</v>
+        <v>45742</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1400,7 +1385,7 @@
         </is>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>45764</v>
+        <v>45768</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1439,7 +1424,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>45908</v>
+        <v>45912</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1543,7 +1528,7 @@
         </is>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1586,7 +1571,7 @@
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1690,7 +1675,7 @@
         </is>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>46288</v>
+        <v>46292</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -1733,7 +1718,7 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>45690</v>
+        <v>45694</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1837,7 +1822,7 @@
         </is>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>45707</v>
+        <v>45711</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1876,7 +1861,7 @@
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>45721</v>
+        <v>45725</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1980,7 +1965,7 @@
         </is>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>45789</v>
+        <v>45793</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -2019,7 +2004,7 @@
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -2123,7 +2108,7 @@
         </is>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>46075</v>
+        <v>46079</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2162,7 +2147,7 @@
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>46200</v>
+        <v>46204</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -2266,7 +2251,7 @@
         </is>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>46288</v>
+        <v>46292</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2305,7 +2290,7 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>45758</v>
+        <v>45762</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -2409,7 +2394,7 @@
         </is>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>45817</v>
+        <v>45821</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2448,7 +2433,7 @@
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2552,7 +2537,7 @@
         </is>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2591,7 +2576,7 @@
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>46232</v>
+        <v>46236</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2695,7 +2680,7 @@
         </is>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>46288</v>
+        <v>46292</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2734,7 +2719,7 @@
         </is>
       </c>
       <c r="G16" s="5" t="n">
-        <v>45724</v>
+        <v>45728</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2838,7 +2823,7 @@
         </is>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>45824</v>
+        <v>45828</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2877,7 +2862,7 @@
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>45718</v>
+        <v>45722</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2981,7 +2966,7 @@
         </is>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>45841</v>
+        <v>45845</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -3024,7 +3009,7 @@
         </is>
       </c>
       <c r="G18" s="5" t="n">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -3128,7 +3113,7 @@
         </is>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>46242</v>
+        <v>46246</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3167,7 +3152,7 @@
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>45966</v>
+        <v>45970</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -3271,7 +3256,7 @@
         </is>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>46000</v>
+        <v>46004</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3310,7 +3295,7 @@
         </is>
       </c>
       <c r="G20" s="5" t="n">
-        <v>45839</v>
+        <v>45843</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -3414,7 +3399,7 @@
         </is>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>45912</v>
+        <v>45916</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3453,7 +3438,7 @@
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>45638</v>
+        <v>45642</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -3557,7 +3542,7 @@
         </is>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>45680</v>
+        <v>45684</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -3600,7 +3585,7 @@
         </is>
       </c>
       <c r="G22" s="5" t="n">
-        <v>46173</v>
+        <v>46177</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -3704,7 +3689,7 @@
         </is>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>46288</v>
+        <v>46292</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -3747,7 +3732,7 @@
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>45652</v>
+        <v>45656</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -3851,7 +3836,7 @@
         </is>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>45832</v>
+        <v>45836</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3890,7 +3875,7 @@
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>46083</v>
+        <v>46087</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -3994,7 +3979,7 @@
         </is>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>46186</v>
+        <v>46190</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -4033,7 +4018,7 @@
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>45693</v>
+        <v>45697</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -4137,7 +4122,7 @@
         </is>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>45805</v>
+        <v>45809</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -4180,7 +4165,7 @@
         </is>
       </c>
       <c r="G26" s="5" t="n">
-        <v>45601</v>
+        <v>45605</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -4284,7 +4269,7 @@
         </is>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>45677</v>
+        <v>45681</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -4323,7 +4308,7 @@
         </is>
       </c>
       <c r="G27" s="5" t="n">
-        <v>45594</v>
+        <v>45598</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -4427,7 +4412,7 @@
         </is>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>45708</v>
+        <v>45712</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4470,7 +4455,7 @@
         </is>
       </c>
       <c r="G28" s="5" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -4574,7 +4559,7 @@
         </is>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>46288</v>
+        <v>46292</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4613,7 +4598,7 @@
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>46088</v>
+        <v>46092</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -4717,7 +4702,7 @@
         </is>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4756,7 +4741,7 @@
         </is>
       </c>
       <c r="G30" s="5" t="n">
-        <v>45812</v>
+        <v>45816</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -4860,7 +4845,7 @@
         </is>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>46005</v>
+        <v>46009</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4903,7 +4888,7 @@
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>45646</v>
+        <v>45650</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -5007,7 +4992,7 @@
         </is>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>45686</v>
+        <v>45690</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -5046,7 +5031,7 @@
         </is>
       </c>
       <c r="G32" s="5" t="n">
-        <v>45810</v>
+        <v>45814</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -5150,7 +5135,7 @@
         </is>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -5193,7 +5178,7 @@
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>45788</v>
+        <v>45792</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -5297,7 +5282,7 @@
         </is>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>45940</v>
+        <v>45944</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
@@ -5446,7 +5431,7 @@
         </is>
       </c>
       <c r="AC34" s="5" t="n">
-        <v>46154</v>
+        <v>46158</v>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
@@ -5487,7 +5472,7 @@
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>45620</v>
+        <v>45624</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -5591,7 +5576,7 @@
         </is>
       </c>
       <c r="AC35" s="5" t="n">
-        <v>45817</v>
+        <v>45821</v>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
@@ -5630,7 +5615,7 @@
         </is>
       </c>
       <c r="G36" s="5" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -5734,7 +5719,7 @@
         </is>
       </c>
       <c r="AC36" s="5" t="n">
-        <v>46288</v>
+        <v>46292</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
@@ -5782,7 +5767,7 @@
         </is>
       </c>
       <c r="G38" s="5" t="n">
-        <v>46245</v>
+        <v>46249</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -5886,7 +5871,7 @@
         </is>
       </c>
       <c r="AC38" s="5" t="n">
-        <v>46288</v>
+        <v>46292</v>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
@@ -5925,7 +5910,7 @@
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>46011</v>
+        <v>46015</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -6029,7 +6014,7 @@
         </is>
       </c>
       <c r="AC39" s="5" t="n">
-        <v>46168</v>
+        <v>46172</v>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
@@ -6068,7 +6053,7 @@
         </is>
       </c>
       <c r="G40" s="5" t="n">
-        <v>45788</v>
+        <v>45792</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -6172,7 +6157,7 @@
         </is>
       </c>
       <c r="AC40" s="5" t="n">
-        <v>45931</v>
+        <v>45935</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
@@ -7339,43 +7324,43 @@
   </mergeCells>
   <dataValidations count="13">
     <dataValidation sqref="E4:E203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Origen de la demanda&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$7</formula1>
+      <formula1>Listas!$E$2:$E$7</formula1>
     </dataValidation>
     <dataValidation sqref="F4:F203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Organismo que toma la MPE&quot;." type="list">
-      <formula1>LISTAS!$D$2:$D$4</formula1>
+      <formula1>Listas!$D$2:$D$4</formula1>
     </dataValidation>
     <dataValidation sqref="H4:H203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Última fecha de renovación&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$7</formula1>
+      <formula1>Listas!$E$2:$E$7</formula1>
     </dataValidation>
     <dataValidation sqref="K4:K203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Elevación dictamen MPE a juzgado&quot;." type="list">
-      <formula1>LISTAS!$F$2:$F$4</formula1>
+      <formula1>Listas!$F$2:$F$4</formula1>
     </dataValidation>
     <dataValidation sqref="L4:L203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Control de legalidad por autoridad judicial&quot;." type="list">
-      <formula1>LISTAS!$F$2:$F$4</formula1>
+      <formula1>Listas!$F$2:$F$4</formula1>
     </dataValidation>
     <dataValidation sqref="M4:M203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Modalidad de cuidado&quot;." type="list">
-      <formula1>LISTAS!$B$2:$B$5</formula1>
+      <formula1>Listas!$B$2:$B$5</formula1>
     </dataValidation>
     <dataValidation sqref="W4:W203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Tipo de proyecto de restitución&quot;." type="list">
-      <formula1>LISTAS!$G$2:$G$5</formula1>
+      <formula1>Listas!$G$2:$G$5</formula1>
     </dataValidation>
     <dataValidation sqref="X4:X203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Decreto judicial de adoptabilidad&quot;." type="list">
-      <formula1>LISTAS!$F$2:$F$4</formula1>
+      <formula1>Listas!$F$2:$F$4</formula1>
     </dataValidation>
     <dataValidation sqref="Y4:Y203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Solicitud inclusión proy. autonomía&quot;." type="list">
-      <formula1>LISTAS!$F$2:$F$4</formula1>
+      <formula1>Listas!$F$2:$F$4</formula1>
     </dataValidation>
     <dataValidation sqref="Z4:Z203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Asiste actualmente a una institución educativa?&quot;." type="list">
-      <formula1>LISTAS!$F$2:$F$4</formula1>
+      <formula1>Listas!$F$2:$F$4</formula1>
     </dataValidation>
     <dataValidation sqref="AA4:AA203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Máximo nivel educativo alcanzado&quot;." type="list">
-      <formula1>LISTAS!$A$2:$A$13</formula1>
+      <formula1>Listas!$A$2:$A$13</formula1>
     </dataValidation>
     <dataValidation sqref="AB4:AB203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Consumo problemático de sustancias&quot;." type="list">
-      <formula1>LISTAS!$F$2:$F$4</formula1>
+      <formula1>Listas!$F$2:$F$4</formula1>
     </dataValidation>
     <dataValidation sqref="AD4:AD203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Motivo de cese&quot;." type="list">
-      <formula1>LISTAS!$C$2:$C$6</formula1>
+      <formula1>Listas!$C$2:$C$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7384,427 +7369,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Campo</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>Indicación para el llenado</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Hoja: MPE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>NyA</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ID del Niño, niña o Adolescente</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Apellido/s</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Nombre/s</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cuil o documento de identidad</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Medida de Protección Expcecional (MPE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Origen de la demanda</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Origen de la demanda".</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Organismo que toma la MPE</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Organismo que toma la MPE".</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Fecha de inicio MPE</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Formato de fecha: dd/mm/aaaa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Última fecha de renovación</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Origen de la demanda".</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Motivo de toma de MPE</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Submotivo de toma de MPE</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Elevación dictamen MPE a juzgado</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Control de legalidad por autoridad judicial</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Modalidad de cuidado</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Modalidad de cuidado".</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Modalidad formal residencial</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ID dispositivo residencial</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Nombre de la residencia/hogar</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Modalidad Formal Familiar</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ID familia</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Familia</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Departamento de residencia de la familia (dispositivo familiar)</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Modalidad Familia Ampliada</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>ID familia ampliada</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Familia Ampliada</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Vínculo con el NyA</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Departamento de residencia de la familia (dispositivo familiar)</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Proyecto de Restitución</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Tipo de proyecto de restitución</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Tipo de proyecto de restitución".</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Decreto judicial de adoptabilidad</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Solicitud inclusión proy. autonomía</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>Situación del NyA</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>¿Asiste actualmente a una institución educativa?</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Máximo nivel educativo alcanzado</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Máximo nivel educativo alcanzado".</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Consumo problemático de sustancias</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>Cese de MPE</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Fecha de cese</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>Formato de fecha: dd/mm/aaaa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Motivo de cese</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Motivo de cese".</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Observaciones</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8073,7 +7637,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8152,7 +7716,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ID del Niño, niña o Adolescente</t>
+          <t>ID del niño, niña o adolescente</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -8227,7 +7791,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ID del Niño, niña o Adolescente</t>
+          <t>ID del niño, niña o adolescente</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
